--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260602.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260602.xlsx
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>24,825,403</t>
+          <t>52,954,331</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>52,954,331</t>
+          <t>24,825,403</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>191,220,396</t>
+          <t>27,942,534</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>27,942,534</t>
+          <t>191,220,396</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
